--- a/fixtures/xlsx/chart-bar/input.xlsx
+++ b/fixtures/xlsx/chart-bar/input.xlsx
@@ -10,19 +10,19 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
-    <t>Revenue</t>
+    <t>Quarter</t>
   </si>
   <si>
     <t>Q1</t>
   </si>
   <si>
-    <t>Q4</t>
-  </si>
-  <si>
     <t>Q2</t>
   </si>
   <si>
-    <t>Quarter</t>
+    <t>Revenue</t>
+  </si>
+  <si>
+    <t>Q4</t>
   </si>
   <si>
     <t>Q3</t>
@@ -168,5 +168,5 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="UTF-8" standalone="yes"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><sheetData><row r="1"><c r="A1" t="s"><v>4</v></c><c r="B1" t="s"><v>0</v></c></row><row r="2"><c r="A2" t="s"><v>1</v></c><c r="B2"><v>10</v></c></row><row r="3"><c r="A3" t="s"><v>3</v></c><c r="B3"><v>20</v></c></row><row r="4"><c r="A4" t="s"><v>5</v></c><c r="B4"><v>15</v></c></row><row r="5"><c r="A5" t="s"><v>2</v></c><c r="B5"><v>25</v></c></row></sheetData><drawing r:id="rId1"/></worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><cols><col min="4" max="12" width="10" customWidth="1"/></cols><sheetData><row r="1"><c r="A1" t="s"><v>0</v></c><c r="B1" t="s"><v>3</v></c></row><row r="2"><c r="A2" t="s"><v>1</v></c><c r="B2"><v>10</v></c></row><row r="3"><c r="A3" t="s"><v>2</v></c><c r="B3"><v>20</v></c></row><row r="4"><c r="A4" t="s"><v>5</v></c><c r="B4"><v>15</v></c></row><row r="5"><c r="A5" t="s"><v>4</v></c><c r="B5"><v>25</v></c></row></sheetData><drawing r:id="rId1"/></worksheet>
 </file>